--- a/outputs_xlsx_solution/simple-dependency.4-wide-NC-1.xlsx
+++ b/outputs_xlsx_solution/simple-dependency.4-wide-NC-1.xlsx
@@ -108,6 +108,12 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -602,10 +608,26 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
         <v>23</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
